--- a/artfynd/A 6165-2026 artfynd.xlsx
+++ b/artfynd/A 6165-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448209</v>
       </c>
       <c r="B2" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448206</v>
       </c>
       <c r="B4" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448208</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448205</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6165-2026 artfynd.xlsx
+++ b/artfynd/A 6165-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448209</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131448204</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448206</v>
       </c>
       <c r="B4" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448208</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448205</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131448210</v>
       </c>
       <c r="B7" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6165-2026 artfynd.xlsx
+++ b/artfynd/A 6165-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448209</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131448204</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448206</v>
       </c>
       <c r="B4" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448208</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448205</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131448210</v>
       </c>
       <c r="B7" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6165-2026 artfynd.xlsx
+++ b/artfynd/A 6165-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131448209</v>
+        <v>131448206</v>
       </c>
       <c r="B2" t="n">
-        <v>79893</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386171</v>
+        <v>386131</v>
       </c>
       <c r="R2" t="n">
-        <v>6758196</v>
+        <v>6758219</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På stubbe med tre brandljud</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448204</v>
+        <v>131448203</v>
       </c>
       <c r="B3" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386140</v>
+        <v>386191</v>
       </c>
       <c r="R3" t="n">
-        <v>6758250</v>
+        <v>6758252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448206</v>
+        <v>131448205</v>
       </c>
       <c r="B4" t="n">
-        <v>78940</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386131</v>
+        <v>386141</v>
       </c>
       <c r="R4" t="n">
-        <v>6758219</v>
+        <v>6758210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,11 +975,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På stubbe med tre brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,11 +1004,11 @@
         <v>131448208</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1113,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448205</v>
+        <v>131448209</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386141</v>
+        <v>386171</v>
       </c>
       <c r="R6" t="n">
-        <v>6758210</v>
+        <v>6758196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131448210</v>
+        <v>131448204</v>
       </c>
       <c r="B7" t="n">
-        <v>57100</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386157</v>
+        <v>386140</v>
       </c>
       <c r="R7" t="n">
-        <v>6758195</v>
+        <v>6758250</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,6 +1324,118 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131448210</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>386157</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6758195</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6165-2026 artfynd.xlsx
+++ b/artfynd/A 6165-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448206</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448205</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448208</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,8 +1471,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>